--- a/Files/Madden26/IE/Season2/FreeAgency/Input/PlayerContract.xlsx
+++ b/Files/Madden26/IE/Season2/FreeAgency/Input/PlayerContract.xlsx
@@ -399,10 +399,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>00101011010011100000000000000000</v>
+        <v>00000000000000000000000011011111</v>
       </c>
       <c r="B2" t="str">
-        <v>00101011010011100000000000000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -419,16 +419,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>00101011010011100000000000000010</v>
+        <v>00000000000000000000000000111011</v>
       </c>
       <c r="B3" t="str">
-        <v>00101011010011100000000000000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -439,16 +439,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>00101011010011100000000000000100</v>
+        <v>00000000000000000000000001010000</v>
       </c>
       <c r="B4" t="str">
-        <v>00101011010011100000000000000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -459,16 +459,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>00101011010011100000000000000110</v>
+        <v>00000000000000000000000001110100</v>
       </c>
       <c r="B5" t="str">
-        <v>00101011010011100000000000000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -479,16 +479,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>00101011010011100000000000001000</v>
+        <v>00000000000000000000000011001001</v>
       </c>
       <c r="B6" t="str">
-        <v>00101011010011100000000000001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C6" t="b">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -499,16 +499,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>00101011010011100000000000001010</v>
+        <v>00000000000000000000000010111011</v>
       </c>
       <c r="B7" t="str">
-        <v>00101011010011100000000000001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -519,16 +519,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>00101011010011100000000000001100</v>
+        <v>00000000000000000000000010001000</v>
       </c>
       <c r="B8" t="str">
-        <v>00101011010011100000000000001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -539,16 +539,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>00101011010011100000000000001110</v>
+        <v>00000000000000000000000000000010</v>
       </c>
       <c r="B9" t="str">
-        <v>00101011010011100000000000001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -559,10 +559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>00101011010011100000000000010000</v>
+        <v>00000000000000000000000001001100</v>
       </c>
       <c r="B10" t="str">
-        <v>00101011010011100000000000010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>00101011010011100000000000010010</v>
+        <v>00000000000000000000000001100111</v>
       </c>
       <c r="B11" t="str">
-        <v>00101011010011100000000000010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -599,16 +599,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>00101011010011100000000000010100</v>
+        <v>00000000000000000000000000101001</v>
       </c>
       <c r="B12" t="str">
-        <v>00101011010011100000000000010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -619,10 +619,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>00101011010011100000000000010110</v>
+        <v>00000000000000000000000001101101</v>
       </c>
       <c r="B13" t="str">
-        <v>00101011010011100000000000010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
@@ -639,16 +639,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>00101011010011100000000000011000</v>
+        <v>00000000000000000000000011110111</v>
       </c>
       <c r="B14" t="str">
-        <v>00101011010011100000000000011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -659,16 +659,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>00101011010011100000000000011010</v>
+        <v>00000000000000000000000001111100</v>
       </c>
       <c r="B15" t="str">
-        <v>00101011010011100000000000011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -679,10 +679,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>00101011010011100000000000011100</v>
+        <v>00000000000000000000000001010010</v>
       </c>
       <c r="B16" t="str">
-        <v>00101011010011100000000000011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>00101011010011100000000000011110</v>
+        <v>00000000000000000000000001101000</v>
       </c>
       <c r="B17" t="str">
-        <v>00101011010011100000000000011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -719,16 +719,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>00101011010011100000000000100000</v>
+        <v>00000000000000000000000000011000</v>
       </c>
       <c r="B18" t="str">
-        <v>00101011010011100000000000100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -739,10 +739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>00101011010011100000000000100010</v>
+        <v>00000000000000000000000011011011</v>
       </c>
       <c r="B19" t="str">
-        <v>00101011010011100000000000100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C19" t="b">
         <v>0</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>00101011010011100000000000100100</v>
+        <v>00000000000000000000000000101010</v>
       </c>
       <c r="B20" t="str">
-        <v>00101011010011100000000000100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
@@ -779,7 +779,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>00000000000000000000000011010111</v>
+        <v>00000000000000000000000000111000</v>
       </c>
       <c r="B21" t="str">
         <v>00000000000000000000000000000000</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -799,16 +799,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>00101011010011100000000000101000</v>
+        <v>00000000000000000000000001001110</v>
       </c>
       <c r="B22" t="str">
-        <v>00101011010011100000000000101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C22" t="b">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -819,16 +819,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>00101011010011100000000000101010</v>
+        <v>00000000000000000000000001001101</v>
       </c>
       <c r="B23" t="str">
-        <v>00101011010011100000000000101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -839,16 +839,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>00101011010011100000000000101100</v>
+        <v>00000000000000000000000001010100</v>
       </c>
       <c r="B24" t="str">
-        <v>00101011010011100000000000101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C24" t="b">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -859,16 +859,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>00101011010011100000000000101110</v>
+        <v>00000000000000000000000000101011</v>
       </c>
       <c r="B25" t="str">
-        <v>00101011010011100000000000101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C25" t="b">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -879,16 +879,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>00101011010011100000000000110000</v>
+        <v>00000000000000000000000100001010</v>
       </c>
       <c r="B26" t="str">
-        <v>00101011010011100000000000110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C26" t="b">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -899,16 +899,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>00101011010011100000000000110010</v>
+        <v>00000000000000000000000000111111</v>
       </c>
       <c r="B27" t="str">
-        <v>00101011010011100000000000110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C27" t="b">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -919,10 +919,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>00101011010011100000000000110100</v>
+        <v>00000000000000000000000001110001</v>
       </c>
       <c r="B28" t="str">
-        <v>00101011010011100000000000110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
@@ -939,16 +939,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>00101011010011100000000000110110</v>
+        <v>00000000000000000000000001110111</v>
       </c>
       <c r="B29" t="str">
-        <v>00101011010011100000000000110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -959,16 +959,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>00101011010011100000000000111000</v>
+        <v>00000000000000000000000000001000</v>
       </c>
       <c r="B30" t="str">
-        <v>00101011010011100000000000111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -979,16 +979,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>00101011010011100000000000111010</v>
+        <v>00000000000000000000000001101010</v>
       </c>
       <c r="B31" t="str">
-        <v>00101011010011100000000000111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C31" t="b">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -999,16 +999,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>00101011010011100000000000111100</v>
+        <v>00000000000000000000000010010010</v>
       </c>
       <c r="B32" t="str">
-        <v>00101011010011100000000000111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1019,16 +1019,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>00101011010011100000000000111110</v>
+        <v>00000000000000000000000000001101</v>
       </c>
       <c r="B33" t="str">
-        <v>00101011010011100000000000111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1039,16 +1039,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>00101011010011100000000001000000</v>
+        <v>00000000000000000000000000101100</v>
       </c>
       <c r="B34" t="str">
-        <v>00101011010011100000000001000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1059,16 +1059,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>00101011010011100000000001000010</v>
+        <v>00000000000000000000000001010001</v>
       </c>
       <c r="B35" t="str">
-        <v>00101011010011100000000001000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>00101011010011100000000001000100</v>
+        <v>00000000000000000000000011100110</v>
       </c>
       <c r="B36" t="str">
-        <v>00101011010011100000000001000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1099,16 +1099,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>00101011010011100000000001000110</v>
+        <v>00000000000000000000000001000101</v>
       </c>
       <c r="B37" t="str">
-        <v>00101011010011100000000001000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>00000000000000000000000011010100</v>
+        <v>00000000000000000000000001110000</v>
       </c>
       <c r="B38" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>00101011010011100000000001001010</v>
+        <v>00000000000000000000000011101010</v>
       </c>
       <c r="B39" t="str">
-        <v>00101011010011100000000001001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C39" t="b">
         <v>0</v>
@@ -1159,16 +1159,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>00101011010011100000000001001100</v>
+        <v>00000000000000000000000000010110</v>
       </c>
       <c r="B40" t="str">
-        <v>00101011010011100000000001001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>00101011010011100000000001001110</v>
+        <v>00000000000000000000000011100001</v>
       </c>
       <c r="B41" t="str">
-        <v>00101011010011100000000001001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
@@ -1199,16 +1199,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>00101011010011100000000001010000</v>
+        <v>00000000000000000000000001010101</v>
       </c>
       <c r="B42" t="str">
-        <v>00101011010011100000000001010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>00101011010011100000000001010010</v>
+        <v>00000000000000000000000000011100</v>
       </c>
       <c r="B43" t="str">
-        <v>00101011010011100000000001010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C43" t="b">
         <v>0</v>
@@ -1239,16 +1239,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>00101011010011100000000001010100</v>
+        <v>00000000000000000000000001011011</v>
       </c>
       <c r="B44" t="str">
-        <v>00101011010011100000000001010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C44" t="b">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1259,16 +1259,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>00101011010011100000000001010110</v>
+        <v>00000000000000000000000000010100</v>
       </c>
       <c r="B45" t="str">
-        <v>00101011010011100000000001010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C45" t="b">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1279,16 +1279,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>00101011010011100000000001011000</v>
+        <v>00000000000000000000000001001010</v>
       </c>
       <c r="B46" t="str">
-        <v>00101011010011100000000001011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C46" t="b">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1299,16 +1299,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>00101011010011100000000001011010</v>
+        <v>00000000000000000000000000111010</v>
       </c>
       <c r="B47" t="str">
-        <v>00101011010011100000000001011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C47" t="b">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1319,16 +1319,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>00101011010011100000000001011100</v>
+        <v>00000000000000000000000010001110</v>
       </c>
       <c r="B48" t="str">
-        <v>00101011010011100000000001011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C48" t="b">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>00101011010011100000000001011110</v>
+        <v>00000000000000000000000011110011</v>
       </c>
       <c r="B49" t="str">
-        <v>00101011010011100000000001011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C49" t="b">
         <v>0</v>
@@ -1359,16 +1359,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>00101011010011100000000001100000</v>
+        <v>00000000000000000000000000111001</v>
       </c>
       <c r="B50" t="str">
-        <v>00101011010011100000000001100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C50" t="b">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>00000000000000000000000100011010</v>
+        <v>00000000000000000000000001111000</v>
       </c>
       <c r="B51" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>00000000000000000000000100011100</v>
+        <v>00000000000000000000000001100010</v>
       </c>
       <c r="B52" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1419,16 +1419,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>00101011010011100000000001100110</v>
+        <v>00000000000000000000000001010111</v>
       </c>
       <c r="B53" t="str">
-        <v>00101011010011100000000001100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1439,16 +1439,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>00101011010011100000000001101000</v>
+        <v>00000000000000000000000000001110</v>
       </c>
       <c r="B54" t="str">
-        <v>00101011010011100000000001101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C54" t="b">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>00000000000000000000000000010011</v>
+        <v>00000000000000000000000001111001</v>
       </c>
       <c r="B55" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>00101011010011100000000001101100</v>
+        <v>00000000000000000000000000100101</v>
       </c>
       <c r="B56" t="str">
-        <v>00101011010011100000000001101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C56" t="b">
         <v>0</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>00000000000000000000000000100100</v>
+        <v>00000000000000000000000001100001</v>
       </c>
       <c r="B57" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -1519,16 +1519,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>00101011010011100000000001110000</v>
+        <v>00000000000000000000000011101101</v>
       </c>
       <c r="B58" t="str">
-        <v>00101011010011100000000001110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C58" t="b">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -1539,16 +1539,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>00101011010011100000000001110010</v>
+        <v>00000000000000000000000010000101</v>
       </c>
       <c r="B59" t="str">
-        <v>00101011010011100000000001110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C59" t="b">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -1559,16 +1559,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>00101011010011100000000001110100</v>
+        <v>00000000000000000000000011101011</v>
       </c>
       <c r="B60" t="str">
-        <v>00101011010011100000000001110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C60" t="b">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -1579,16 +1579,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>00101011010011100000000001110110</v>
+        <v>00000000000000000000000000100000</v>
       </c>
       <c r="B61" t="str">
-        <v>00101011010011100000000001110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C61" t="b">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -1599,16 +1599,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>00101011010011100000000001111000</v>
+        <v>00000000000000000000000001000000</v>
       </c>
       <c r="B62" t="str">
-        <v>00101011010011100000000001111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C62" t="b">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>00101011010011100000000001111010</v>
+        <v>00000000000000000000000001011101</v>
       </c>
       <c r="B63" t="str">
-        <v>00101011010011100000000001111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C63" t="b">
         <v>0</v>
@@ -1639,16 +1639,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>00101011010011100000000001111100</v>
+        <v>00000000000000000000000011001111</v>
       </c>
       <c r="B64" t="str">
-        <v>00101011010011100000000001111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C64" t="b">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -1659,16 +1659,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>00101011010011100000000001111110</v>
+        <v>00000000000000000000000000111100</v>
       </c>
       <c r="B65" t="str">
-        <v>00101011010011100000000001111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C65" t="b">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>00101011010011100000000010000000</v>
+        <v>00000000000000000000000001101111</v>
       </c>
       <c r="B66" t="str">
-        <v>00101011010011100000000010000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C66" t="b">
         <v>0</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>00101011010011100000000010000010</v>
+        <v>00000000000000000000000000110011</v>
       </c>
       <c r="B67" t="str">
-        <v>00101011010011100000000010000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C67" t="b">
         <v>0</v>
@@ -1719,16 +1719,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>00101011010011100000000010000100</v>
+        <v>00000000000000000000000011010010</v>
       </c>
       <c r="B68" t="str">
-        <v>00101011010011100000000010000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C68" t="b">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -1739,16 +1739,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>00101011010011100000000010000110</v>
+        <v>00000000000000000000000000011011</v>
       </c>
       <c r="B69" t="str">
-        <v>00101011010011100000000010000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C69" t="b">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -1759,16 +1759,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>00101011010011100000000010001000</v>
+        <v>00000000000000000000000000111101</v>
       </c>
       <c r="B70" t="str">
-        <v>00101011010011100000000010001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C70" t="b">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -1779,16 +1779,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>00101011010011100000000010001010</v>
+        <v>00000000000000000000000001110011</v>
       </c>
       <c r="B71" t="str">
-        <v>00101011010011100000000010001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C71" t="b">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -1799,16 +1799,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>00101011010011100000000010001100</v>
+        <v>00000000000000000000000000001100</v>
       </c>
       <c r="B72" t="str">
-        <v>00101011010011100000000010001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C72" t="b">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -1819,16 +1819,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>00101011010011100000000010001110</v>
+        <v>00000000000000000000000000000001</v>
       </c>
       <c r="B73" t="str">
-        <v>00101011010011100000000010001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C73" t="b">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -1839,16 +1839,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>00101011010011100000000010010000</v>
+        <v>00000000000000000000000011010110</v>
       </c>
       <c r="B74" t="str">
-        <v>00101011010011100000000010010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C74" t="b">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>00101011010011100000000010010010</v>
+        <v>00000000000000000000000000100100</v>
       </c>
       <c r="B75" t="str">
-        <v>00101011010011100000000010010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C75" t="b">
         <v>0</v>
@@ -1879,16 +1879,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>00101011010011100000000010010100</v>
+        <v>00000000000000000000000001001011</v>
       </c>
       <c r="B76" t="str">
-        <v>00101011010011100000000010010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C76" t="b">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1899,16 +1899,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>00101011010011100000000010010110</v>
+        <v>00000000000000000000000000010101</v>
       </c>
       <c r="B77" t="str">
-        <v>00101011010011100000000010010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C77" t="b">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -1919,16 +1919,16 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>00101011010011100000000010011000</v>
+        <v>00000000000000000000000001000001</v>
       </c>
       <c r="B78" t="str">
-        <v>00101011010011100000000010011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C78" t="b">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -1939,16 +1939,16 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>00101011010011100000000010011010</v>
+        <v>00000000000000000000000001111101</v>
       </c>
       <c r="B79" t="str">
-        <v>00101011010011100000000010011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C79" t="b">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -1959,16 +1959,16 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>00101011010011100000000010011100</v>
+        <v>00000000000000000000000010000010</v>
       </c>
       <c r="B80" t="str">
-        <v>00101011010011100000000010011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C80" t="b">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -1979,16 +1979,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>00101011010011100000000010011110</v>
+        <v>00000000000000000000000000110100</v>
       </c>
       <c r="B81" t="str">
-        <v>00101011010011100000000010011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C81" t="b">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -1999,16 +1999,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>00101011010011100000000010100000</v>
+        <v>00000000000000000000000000000110</v>
       </c>
       <c r="B82" t="str">
-        <v>00101011010011100000000010100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C82" t="b">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2019,16 +2019,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>00101011010011100000000010100010</v>
+        <v>00000000000000000000000001110010</v>
       </c>
       <c r="B83" t="str">
-        <v>00101011010011100000000010100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C83" t="b">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>00101011010011100000000010100100</v>
+        <v>00000000000000000000000001010011</v>
       </c>
       <c r="B84" t="str">
-        <v>00101011010011100000000010100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C84" t="b">
         <v>0</v>
@@ -2059,16 +2059,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>00101011010011100000000010100110</v>
+        <v>00000000000000000000000000101000</v>
       </c>
       <c r="B85" t="str">
-        <v>00101011010011100000000010100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C85" t="b">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -2079,16 +2079,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>00101011010011100000000010101000</v>
+        <v>00000000000000000000000011011010</v>
       </c>
       <c r="B86" t="str">
-        <v>00101011010011100000000010101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C86" t="b">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -2099,16 +2099,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>00101011010011100000000010101010</v>
+        <v>00000000000000000000000001010110</v>
       </c>
       <c r="B87" t="str">
-        <v>00101011010011100000000010101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C87" t="b">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>00101011010011100000000010101100</v>
+        <v>00000000000000000000000001110101</v>
       </c>
       <c r="B88" t="str">
-        <v>00101011010011100000000010101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C88" t="b">
         <v>0</v>
@@ -2139,7 +2139,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>00000000000000000000000000110101</v>
+        <v>00000000000000000000000001001001</v>
       </c>
       <c r="B89" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -2159,16 +2159,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>00101011010011100000000010110000</v>
+        <v>00000000000000000000000011110010</v>
       </c>
       <c r="B90" t="str">
-        <v>00101011010011100000000010110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C90" t="b">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -2179,16 +2179,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>00101011010011100000000010110010</v>
+        <v>00000000000000000000000001110110</v>
       </c>
       <c r="B91" t="str">
-        <v>00101011010011100000000010110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C91" t="b">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -2199,16 +2199,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>00101011010011100000000010110100</v>
+        <v>00000000000000000000000010111100</v>
       </c>
       <c r="B92" t="str">
-        <v>00101011010011100000000010110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C92" t="b">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -2219,16 +2219,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>00101011010011100000000010110110</v>
+        <v>00000000000000000000000000110110</v>
       </c>
       <c r="B93" t="str">
-        <v>00101011010011100000000010110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C93" t="b">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -2239,16 +2239,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>00101011010011100000000010111000</v>
+        <v>00000000000000000000000001100110</v>
       </c>
       <c r="B94" t="str">
-        <v>00101011010011100000000010111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C94" t="b">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>00101011010011100000000010111010</v>
+        <v>00000000000000000000000000010011</v>
       </c>
       <c r="B95" t="str">
-        <v>00101011010011100000000010111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C95" t="b">
         <v>0</v>
@@ -2279,16 +2279,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>00101011010011100000000010111100</v>
+        <v>00000000000000000000000000011010</v>
       </c>
       <c r="B96" t="str">
-        <v>00101011010011100000000010111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C96" t="b">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -2299,16 +2299,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>00101011010011100000000010111110</v>
+        <v>00000000000000000000000000110101</v>
       </c>
       <c r="B97" t="str">
-        <v>00101011010011100000000010111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C97" t="b">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>00101011010011100000000011000000</v>
+        <v>00000000000000000000000011110100</v>
       </c>
       <c r="B98" t="str">
-        <v>00101011010011100000000011000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C98" t="b">
         <v>0</v>
@@ -2339,16 +2339,16 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>00101011010011100000000011000010</v>
+        <v>00000000000000000000000001100011</v>
       </c>
       <c r="B99" t="str">
-        <v>00101011010011100000000011000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C99" t="b">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -2359,16 +2359,16 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>00101011010011100000000011000100</v>
+        <v>00000000000000000000000000110001</v>
       </c>
       <c r="B100" t="str">
-        <v>00101011010011100000000011000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C100" t="b">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -2379,16 +2379,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>00101011010011100000000011000110</v>
+        <v>00000000000000000000000000101110</v>
       </c>
       <c r="B101" t="str">
-        <v>00101011010011100000000011000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C101" t="b">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -2399,16 +2399,16 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>00101011010011100000000011001000</v>
+        <v>00000000000000000000000010111110</v>
       </c>
       <c r="B102" t="str">
-        <v>00101011010011100000000011001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C102" t="b">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>00101011010011100000000011001010</v>
+        <v>00000000000000000000000011011100</v>
       </c>
       <c r="B103" t="str">
-        <v>00101011010011100000000011001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C103" t="b">
         <v>0</v>
@@ -2439,16 +2439,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>00101011010011100000000011001100</v>
+        <v>00000000000000000000000010001011</v>
       </c>
       <c r="B104" t="str">
-        <v>00101011010011100000000011001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C104" t="b">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -2459,16 +2459,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>00101011010011100000000011001110</v>
+        <v>00000000000000000000000000001010</v>
       </c>
       <c r="B105" t="str">
-        <v>00101011010011100000000011001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C105" t="b">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -2479,16 +2479,16 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>00101011010011100000000011010000</v>
+        <v>00000000000000000000000011101111</v>
       </c>
       <c r="B106" t="str">
-        <v>00101011010011100000000011010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C106" t="b">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -2499,16 +2499,16 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>00101011010011100000000011010010</v>
+        <v>00000000000000000000000010001100</v>
       </c>
       <c r="B107" t="str">
-        <v>00101011010011100000000011010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C107" t="b">
         <v>0</v>
       </c>
       <c r="D107">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>00101011010011100000000011010100</v>
+        <v>00000000000000000000000000001001</v>
       </c>
       <c r="B108" t="str">
-        <v>00101011010011100000000011010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C108" t="b">
         <v>0</v>
@@ -2539,16 +2539,16 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>00101011010011100000000011010110</v>
+        <v>00000000000000000000000000001011</v>
       </c>
       <c r="B109" t="str">
-        <v>00101011010011100000000011010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C109" t="b">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -2559,16 +2559,16 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>00101011010011100000000011011000</v>
+        <v>00000000000000000000000001101110</v>
       </c>
       <c r="B110" t="str">
-        <v>00101011010011100000000011011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C110" t="b">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>00000000000000000000000011100001</v>
+        <v>00000000000000000000000000101101</v>
       </c>
       <c r="B111" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -2599,16 +2599,16 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>00101011010011100000000011011100</v>
+        <v>00000000000000000000000011101000</v>
       </c>
       <c r="B112" t="str">
-        <v>00101011010011100000000011011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C112" t="b">
         <v>0</v>
       </c>
       <c r="D112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -2619,16 +2619,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>00101011010011100000000011011110</v>
+        <v>00000000000000000000000001000011</v>
       </c>
       <c r="B113" t="str">
-        <v>00101011010011100000000011011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C113" t="b">
         <v>0</v>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -2639,16 +2639,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>00101011010011100000000011100000</v>
+        <v>00000000000000000000000000110111</v>
       </c>
       <c r="B114" t="str">
-        <v>00101011010011100000000011100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C114" t="b">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>00101011010011100000000011100010</v>
+        <v>00000000000000000000000011000011</v>
       </c>
       <c r="B115" t="str">
-        <v>00101011010011100000000011100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C115" t="b">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>00101011010011100000000011100100</v>
+        <v>00000000000000000000000001111110</v>
       </c>
       <c r="B116" t="str">
-        <v>00101011010011100000000011100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C116" t="b">
         <v>0</v>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -2699,16 +2699,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>00101011010011100000000011100110</v>
+        <v>00000000000000000000000011101100</v>
       </c>
       <c r="B117" t="str">
-        <v>00101011010011100000000011100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C117" t="b">
         <v>0</v>
       </c>
       <c r="D117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -2719,16 +2719,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>00101011010011100000000011101000</v>
+        <v>00000000000000000000000001000010</v>
       </c>
       <c r="B118" t="str">
-        <v>00101011010011100000000011101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C118" t="b">
         <v>0</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -2739,16 +2739,16 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>00101011010011100000000011101010</v>
+        <v>00000000000000000000000010001001</v>
       </c>
       <c r="B119" t="str">
-        <v>00101011010011100000000011101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C119" t="b">
         <v>0</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -2759,16 +2759,16 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>00101011010011100000000011101100</v>
+        <v>00000000000000000000000000000100</v>
       </c>
       <c r="B120" t="str">
-        <v>00101011010011100000000011101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C120" t="b">
         <v>0</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>00000000000000000000000010101111</v>
+        <v>00000000000000000000000011011001</v>
       </c>
       <c r="B121" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -2799,16 +2799,16 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>00101011010011100000000011110000</v>
+        <v>00000000000000000000000000100110</v>
       </c>
       <c r="B122" t="str">
-        <v>00101011010011100000000011110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C122" t="b">
         <v>0</v>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -2819,16 +2819,16 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>00101011010011100000000011110010</v>
+        <v>00000000000000000000000000110010</v>
       </c>
       <c r="B123" t="str">
-        <v>00101011010011100000000011110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C123" t="b">
         <v>0</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>00101011010011100000000011110100</v>
+        <v>00000000000000000000000010001101</v>
       </c>
       <c r="B124" t="str">
-        <v>00101011010011100000000011110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C124" t="b">
         <v>0</v>
@@ -2859,16 +2859,16 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>00101011010011100000000011110110</v>
+        <v>00000000000000000000000011000100</v>
       </c>
       <c r="B125" t="str">
-        <v>00101011010011100000000011110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C125" t="b">
         <v>0</v>
       </c>
       <c r="D125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>00101011010011100000000011111000</v>
+        <v>00000000000000000000000000000111</v>
       </c>
       <c r="B126" t="str">
-        <v>00101011010011100000000011111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C126" t="b">
         <v>0</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>00101011010011100000000011111010</v>
+        <v>00000000000000000000000001001111</v>
       </c>
       <c r="B127" t="str">
-        <v>00101011010011100000000011111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C127" t="b">
         <v>0</v>
@@ -2919,16 +2919,16 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>00101011010011100000000011111100</v>
+        <v>00000000000000000000000001101100</v>
       </c>
       <c r="B128" t="str">
-        <v>00101011010011100000000011111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C128" t="b">
         <v>0</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -2939,16 +2939,16 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>00101011010011100000000011111110</v>
+        <v>00000000000000000000000010101000</v>
       </c>
       <c r="B129" t="str">
-        <v>00101011010011100000000011111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C129" t="b">
         <v>0</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -2959,16 +2959,16 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>00101011010011100000000100000000</v>
+        <v>00000000000000000000000001101001</v>
       </c>
       <c r="B130" t="str">
-        <v>00101011010011100000000100000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C130" t="b">
         <v>0</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -2979,16 +2979,16 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>00101011010011100000000100000010</v>
+        <v>00000000000000000000000011000000</v>
       </c>
       <c r="B131" t="str">
-        <v>00101011010011100000000100000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C131" t="b">
         <v>0</v>
       </c>
       <c r="D131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -2999,16 +2999,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>00101011010011100000000100000100</v>
+        <v>00000000000000000000000010000011</v>
       </c>
       <c r="B132" t="str">
-        <v>00101011010011100000000100000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C132" t="b">
         <v>0</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>00101011010011100000000100000110</v>
+        <v>00000000000000000000000001100101</v>
       </c>
       <c r="B133" t="str">
-        <v>00101011010011100000000100000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C133" t="b">
         <v>0</v>
@@ -3039,16 +3039,16 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>00101011010011100000000100001000</v>
+        <v>00000000000000000000000011110110</v>
       </c>
       <c r="B134" t="str">
-        <v>00101011010011100000000100001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C134" t="b">
         <v>0</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -3059,16 +3059,16 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>00101011010011100000000100001010</v>
+        <v>00000000000000000000000010000110</v>
       </c>
       <c r="B135" t="str">
-        <v>00101011010011100000000100001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C135" t="b">
         <v>0</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -3079,16 +3079,16 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>00101011010011100000000100001100</v>
+        <v>00000000000000000000000001111111</v>
       </c>
       <c r="B136" t="str">
-        <v>00101011010011100000000100001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C136" t="b">
         <v>0</v>
       </c>
       <c r="D136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -3099,16 +3099,16 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>00101011010011100000000100001110</v>
+        <v>00000000000000000000000010010111</v>
       </c>
       <c r="B137" t="str">
-        <v>00101011010011100000000100001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C137" t="b">
         <v>0</v>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -3119,16 +3119,16 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>00101011010011100000000100010000</v>
+        <v>00000000000000000000000000010111</v>
       </c>
       <c r="B138" t="str">
-        <v>00101011010011100000000100010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C138" t="b">
         <v>0</v>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -3139,16 +3139,16 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>00101011010011100000000100010010</v>
+        <v>00000000000000000000000010010001</v>
       </c>
       <c r="B139" t="str">
-        <v>00101011010011100000000100010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C139" t="b">
         <v>0</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>00101011010011100000000100010100</v>
+        <v>00000000000000000000000000100011</v>
       </c>
       <c r="B140" t="str">
-        <v>00101011010011100000000100010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C140" t="b">
         <v>0</v>
@@ -3179,16 +3179,16 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>00101011010011100000000100010110</v>
+        <v>00000000000000000000000010010011</v>
       </c>
       <c r="B141" t="str">
-        <v>00101011010011100000000100010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C141" t="b">
         <v>0</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>00101011010011100000000100011000</v>
+        <v>00000000000000000000000011110101</v>
       </c>
       <c r="B142" t="str">
-        <v>00101011010011100000000100011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C142" t="b">
         <v>0</v>
@@ -3219,16 +3219,16 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>00101011010011100000000100011010</v>
+        <v>00000000000000000000000001011100</v>
       </c>
       <c r="B143" t="str">
-        <v>00101011010011100000000100011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C143" t="b">
         <v>0</v>
       </c>
       <c r="D143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -3239,16 +3239,16 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>00101011010011100000000100011100</v>
+        <v>00000000000000000000000000010010</v>
       </c>
       <c r="B144" t="str">
-        <v>00101011010011100000000100011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C144" t="b">
         <v>0</v>
       </c>
       <c r="D144">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -3259,16 +3259,16 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>00101011010011100000000100011110</v>
+        <v>00000000000000000000000000001111</v>
       </c>
       <c r="B145" t="str">
-        <v>00101011010011100000000100011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C145" t="b">
         <v>0</v>
       </c>
       <c r="D145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -3279,16 +3279,16 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>00101011010011100000000100100000</v>
+        <v>00000000000000000000000000111110</v>
       </c>
       <c r="B146" t="str">
-        <v>00101011010011100000000100100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C146" t="b">
         <v>0</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -3299,16 +3299,16 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>00101011010011100000000100100010</v>
+        <v>00000000000000000000000001111010</v>
       </c>
       <c r="B147" t="str">
-        <v>00101011010011100000000100100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C147" t="b">
         <v>0</v>
       </c>
       <c r="D147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>00101011010011100000000100100100</v>
+        <v>00000000000000000000000010000001</v>
       </c>
       <c r="B148" t="str">
-        <v>00101011010011100000000100100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C148" t="b">
         <v>0</v>
@@ -3339,16 +3339,16 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>00101011010011100000000100100110</v>
+        <v>00000000000000000000000001011111</v>
       </c>
       <c r="B149" t="str">
-        <v>00101011010011100000000100100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C149" t="b">
         <v>0</v>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -3359,16 +3359,16 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>00101011010011100000000100101000</v>
+        <v>00000000000000000000000011010101</v>
       </c>
       <c r="B150" t="str">
-        <v>00101011010011100000000100101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C150" t="b">
         <v>0</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -3379,16 +3379,16 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>00101011010011100000000100101010</v>
+        <v>00000000000000000000000010000111</v>
       </c>
       <c r="B151" t="str">
-        <v>00101011010011100000000100101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C151" t="b">
         <v>0</v>
       </c>
       <c r="D151">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -3399,16 +3399,16 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>00101011010011100000000100101100</v>
+        <v>00000000000000000000000011010001</v>
       </c>
       <c r="B152" t="str">
-        <v>00101011010011100000000100101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C152" t="b">
         <v>0</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -3419,16 +3419,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>00101011010011100000000100101110</v>
+        <v>00000000000000000000000010101010</v>
       </c>
       <c r="B153" t="str">
-        <v>00101011010011100000000100101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C153" t="b">
         <v>0</v>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -3439,16 +3439,16 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>00101011010011100000000100110000</v>
+        <v>00000000000000000000000011001101</v>
       </c>
       <c r="B154" t="str">
-        <v>00101011010011100000000100110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C154" t="b">
         <v>0</v>
       </c>
       <c r="D154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -3459,16 +3459,16 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>00101011010011100000000100110010</v>
+        <v>00000000000000000000000100001000</v>
       </c>
       <c r="B155" t="str">
-        <v>00101011010011100000000100110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C155" t="b">
         <v>0</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -3479,16 +3479,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>00101011010011100000000100110100</v>
+        <v>00000000000000000000000011011110</v>
       </c>
       <c r="B156" t="str">
-        <v>00101011010011100000000100110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C156" t="b">
         <v>0</v>
       </c>
       <c r="D156">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -3499,16 +3499,16 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>00101011010011100000000100110110</v>
+        <v>00000000000000000000000010011010</v>
       </c>
       <c r="B157" t="str">
-        <v>00101011010011100000000100110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C157" t="b">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>00101011010011100000000100111000</v>
+        <v>00000000000000000000000010011011</v>
       </c>
       <c r="B158" t="str">
-        <v>00101011010011100000000100111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C158" t="b">
         <v>0</v>
@@ -3539,16 +3539,16 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>00101011010011100000000100111010</v>
+        <v>00000000000000000000000000010000</v>
       </c>
       <c r="B159" t="str">
-        <v>00101011010011100000000100111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C159" t="b">
         <v>0</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -3559,16 +3559,16 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>00101011010011100000000100111100</v>
+        <v>00000000000000000000000010111010</v>
       </c>
       <c r="B160" t="str">
-        <v>00101011010011100000000100111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C160" t="b">
         <v>0</v>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -3579,16 +3579,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>00101011010011100000000100111110</v>
+        <v>00000000000000000000000011000001</v>
       </c>
       <c r="B161" t="str">
-        <v>00101011010011100000000100111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C161" t="b">
         <v>0</v>
       </c>
       <c r="D161">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -3599,7 +3599,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>00000000000000000000000010110001</v>
+        <v>00000000000000000000000001011010</v>
       </c>
       <c r="B162" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>00101011010011100000000101000010</v>
+        <v>00000000000000000000000010111111</v>
       </c>
       <c r="B163" t="str">
-        <v>00101011010011100000000101000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C163" t="b">
         <v>0</v>
@@ -3639,16 +3639,16 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>00101011010011100000000101000100</v>
+        <v>00000000000000000000000010100001</v>
       </c>
       <c r="B164" t="str">
-        <v>00101011010011100000000101000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C164" t="b">
         <v>0</v>
       </c>
       <c r="D164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -3659,16 +3659,16 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>00101011010011100000000101000110</v>
+        <v>00000000000000000000000011000111</v>
       </c>
       <c r="B165" t="str">
-        <v>00101011010011100000000101000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C165" t="b">
         <v>0</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -3679,16 +3679,16 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>00101011010011100000000101001000</v>
+        <v>00000000000000000000000011100011</v>
       </c>
       <c r="B166" t="str">
-        <v>00101011010011100000000101001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C166" t="b">
         <v>0</v>
       </c>
       <c r="D166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>00000000000000000000000000110001</v>
+        <v>00000000000000000000000010100111</v>
       </c>
       <c r="B167" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -3719,16 +3719,16 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>00101011010011100000000101001100</v>
+        <v>00000000000000000000000010100101</v>
       </c>
       <c r="B168" t="str">
-        <v>00101011010011100000000101001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C168" t="b">
         <v>0</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -3739,16 +3739,16 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>00101011010011100000000101001110</v>
+        <v>00000000000000000000000011001011</v>
       </c>
       <c r="B169" t="str">
-        <v>00101011010011100000000101001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C169" t="b">
         <v>0</v>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -3759,16 +3759,16 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>00101011010011100000000101010000</v>
+        <v>00000000000000000000000010010100</v>
       </c>
       <c r="B170" t="str">
-        <v>00101011010011100000000101010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C170" t="b">
         <v>0</v>
       </c>
       <c r="D170">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>00101011010011100000000101010010</v>
+        <v>00000000000000000000000010110101</v>
       </c>
       <c r="B171" t="str">
-        <v>00101011010011100000000101010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C171" t="b">
         <v>0</v>
@@ -3799,16 +3799,16 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>00101011010011100000000101010100</v>
+        <v>00000000000000000000000001111011</v>
       </c>
       <c r="B172" t="str">
-        <v>00101011010011100000000101010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C172" t="b">
         <v>0</v>
       </c>
       <c r="D172">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -3819,10 +3819,10 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>00101011010011100000000101010110</v>
+        <v>00000000000000000000000011100000</v>
       </c>
       <c r="B173" t="str">
-        <v>00101011010011100000000101010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C173" t="b">
         <v>0</v>
@@ -3839,16 +3839,16 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>00101011010011100000000101011000</v>
+        <v>00000000000000000000000010101011</v>
       </c>
       <c r="B174" t="str">
-        <v>00101011010011100000000101011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C174" t="b">
         <v>0</v>
       </c>
       <c r="D174">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -3859,16 +3859,16 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>00101011010011100000000101011010</v>
+        <v>00000000000000000000000010101100</v>
       </c>
       <c r="B175" t="str">
-        <v>00101011010011100000000101011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C175" t="b">
         <v>0</v>
       </c>
       <c r="D175">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -3879,16 +3879,16 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>00101011010011100000000101011100</v>
+        <v>00000000000000000000000010011001</v>
       </c>
       <c r="B176" t="str">
-        <v>00101011010011100000000101011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C176" t="b">
         <v>0</v>
       </c>
       <c r="D176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>00000000000000000000000011110010</v>
+        <v>00000000000000000000000010100011</v>
       </c>
       <c r="B177" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>00000000000000000000000001101101</v>
+        <v>00000000000000000000000000000101</v>
       </c>
       <c r="B178" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3928,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>00000000000000000000000100101100</v>
+        <v>00000000000000000000000011000101</v>
       </c>
       <c r="B179" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>00101011010011100000000101100100</v>
+        <v>00000000000000000000000010110001</v>
       </c>
       <c r="B180" t="str">
-        <v>00101011010011100000000101100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C180" t="b">
         <v>0</v>
@@ -3979,16 +3979,16 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>00101011010011100000000101100110</v>
+        <v>00000000000000000000000010110010</v>
       </c>
       <c r="B181" t="str">
-        <v>00101011010011100000000101100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C181" t="b">
         <v>0</v>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -3999,16 +3999,16 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>00101011010011100000000101101000</v>
+        <v>00000000000000000000000010110011</v>
       </c>
       <c r="B182" t="str">
-        <v>00101011010011100000000101101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C182" t="b">
         <v>0</v>
       </c>
       <c r="D182">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -4019,16 +4019,16 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>00101011010011100000000101101010</v>
+        <v>00000000000000000000000010100000</v>
       </c>
       <c r="B183" t="str">
-        <v>00101011010011100000000101101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C183" t="b">
         <v>0</v>
       </c>
       <c r="D183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -4039,16 +4039,16 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>00101011010011100000000101101100</v>
+        <v>00000000000000000000000011110000</v>
       </c>
       <c r="B184" t="str">
-        <v>00101011010011100000000101101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C184" t="b">
         <v>0</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -4059,10 +4059,10 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>00101011010011100000000101101110</v>
+        <v>00000000000000000000000010110110</v>
       </c>
       <c r="B185" t="str">
-        <v>00101011010011100000000101101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C185" t="b">
         <v>0</v>
@@ -4079,16 +4079,16 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>00101011010011100000000101110000</v>
+        <v>00000000000000000000000010100110</v>
       </c>
       <c r="B186" t="str">
-        <v>00101011010011100000000101110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C186" t="b">
         <v>0</v>
       </c>
       <c r="D186">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -4099,16 +4099,16 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>00101011010011100000000101110010</v>
+        <v>00000000000000000000000011100100</v>
       </c>
       <c r="B187" t="str">
-        <v>00101011010011100000000101110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C187" t="b">
         <v>0</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -4119,10 +4119,10 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>00101011010011100000000101110100</v>
+        <v>00000000000000000000000010111001</v>
       </c>
       <c r="B188" t="str">
-        <v>00101011010011100000000101110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C188" t="b">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>00000000000000000000000100000001</v>
+        <v>00000000000000000000000010011101</v>
       </c>
       <c r="B189" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4159,16 +4159,16 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>00101011010011100000000101111000</v>
+        <v>00000000000000000000000011010011</v>
       </c>
       <c r="B190" t="str">
-        <v>00101011010011100000000101111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C190" t="b">
         <v>0</v>
       </c>
       <c r="D190">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>00101011010011100000000101111010</v>
+        <v>00000000000000000000000010110000</v>
       </c>
       <c r="B191" t="str">
-        <v>00101011010011100000000101111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C191" t="b">
         <v>0</v>
@@ -4199,16 +4199,16 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>00101011010011100000000101111100</v>
+        <v>00000000000000000000000011010111</v>
       </c>
       <c r="B192" t="str">
-        <v>00101011010011100000000101111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C192" t="b">
         <v>0</v>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -4219,7 +4219,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>00000000000000000000000010111011</v>
+        <v>00000000000000000000000010011111</v>
       </c>
       <c r="B193" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -4239,16 +4239,16 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>00101011010011100000000110000000</v>
+        <v>00000000000000000000000001101011</v>
       </c>
       <c r="B194" t="str">
-        <v>00101011010011100000000110000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C194" t="b">
         <v>0</v>
       </c>
       <c r="D194">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -4259,16 +4259,16 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>00101011010011100000000110000010</v>
+        <v>00000000000000000000000011010100</v>
       </c>
       <c r="B195" t="str">
-        <v>00101011010011100000000110000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C195" t="b">
         <v>0</v>
       </c>
       <c r="D195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>00101011010011100000000110000100</v>
+        <v>00000000000000000000000011100111</v>
       </c>
       <c r="B196" t="str">
-        <v>00101011010011100000000110000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C196" t="b">
         <v>0</v>
@@ -4299,7 +4299,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>00000000000000000000000011011100</v>
+        <v>00000000000000000000000001001000</v>
       </c>
       <c r="B197" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -4319,16 +4319,16 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>00101011010011100000000110001000</v>
+        <v>00000000000000000000000000010001</v>
       </c>
       <c r="B198" t="str">
-        <v>00101011010011100000000110001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C198" t="b">
         <v>0</v>
       </c>
       <c r="D198">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -4339,16 +4339,16 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>00101011010011100000000110001010</v>
+        <v>00000000000000000000000010101110</v>
       </c>
       <c r="B199" t="str">
-        <v>00101011010011100000000110001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C199" t="b">
         <v>0</v>
       </c>
       <c r="D199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>00101011010011100000000110001100</v>
+        <v>00000000000000000000000010100100</v>
       </c>
       <c r="B200" t="str">
-        <v>00101011010011100000000110001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C200" t="b">
         <v>0</v>
@@ -4379,7 +4379,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>00000000000000000000000011111111</v>
+        <v>00000000000000000000000010111000</v>
       </c>
       <c r="B201" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>00000000000000000000000010100101</v>
+        <v>00000000000000000000000000100001</v>
       </c>
       <c r="B202" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>00101011010011100000000110010010</v>
+        <v>00000000000000000000000010000000</v>
       </c>
       <c r="B203" t="str">
-        <v>00101011010011100000000110010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C203" t="b">
         <v>0</v>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>00101011010011100000000110010100</v>
+        <v>00000000000000000000000011001110</v>
       </c>
       <c r="B204" t="str">
-        <v>00101011010011100000000110010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C204" t="b">
         <v>0</v>
@@ -4459,16 +4459,16 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>00101011010011100000000110010110</v>
+        <v>00000000000000000000000000110000</v>
       </c>
       <c r="B205" t="str">
-        <v>00101011010011100000000110010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C205" t="b">
         <v>0</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>00101011010011100000000110011000</v>
+        <v>00000000000000000000000010101001</v>
       </c>
       <c r="B206" t="str">
-        <v>00101011010011100000000110011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C206" t="b">
         <v>0</v>
@@ -4499,16 +4499,16 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>00101011010011100000000110011010</v>
+        <v>00000000000000000000000010010110</v>
       </c>
       <c r="B207" t="str">
-        <v>00101011010011100000000110011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C207" t="b">
         <v>0</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -4519,10 +4519,10 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>00101011010011100000000110011100</v>
+        <v>00000000000000000000000010001111</v>
       </c>
       <c r="B208" t="str">
-        <v>00101011010011100000000110011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C208" t="b">
         <v>0</v>
@@ -4539,16 +4539,16 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>00101011010011100000000110011110</v>
+        <v>00000000000000000000000010000100</v>
       </c>
       <c r="B209" t="str">
-        <v>00101011010011100000000110011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C209" t="b">
         <v>0</v>
       </c>
       <c r="D209">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -4559,10 +4559,10 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>00101011010011100000000110100000</v>
+        <v>00000000000000000000000011100010</v>
       </c>
       <c r="B210" t="str">
-        <v>00101011010011100000000110100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C210" t="b">
         <v>0</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>00101011010011100000000110100010</v>
+        <v>00000000000000000000000000100010</v>
       </c>
       <c r="B211" t="str">
-        <v>00101011010011100000000110100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C211" t="b">
         <v>0</v>
@@ -4599,10 +4599,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>00101011010011100000000110100100</v>
+        <v>00000000000000000000000001011110</v>
       </c>
       <c r="B212" t="str">
-        <v>00101011010011100000000110100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C212" t="b">
         <v>0</v>
@@ -4619,7 +4619,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>00000000000000000000000010111111</v>
+        <v>00000000000000000000000010011110</v>
       </c>
       <c r="B213" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>00000000000000000000000100101001</v>
+        <v>00000000000000000000000010011100</v>
       </c>
       <c r="B214" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4659,16 +4659,16 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>00101011010011100000000110101010</v>
+        <v>00000000000000000000000010010101</v>
       </c>
       <c r="B215" t="str">
-        <v>00101011010011100000000110101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C215" t="b">
         <v>0</v>
       </c>
       <c r="D215">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -4679,16 +4679,16 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>00101011010011100000000110101100</v>
+        <v>00000000000000000000000001100100</v>
       </c>
       <c r="B216" t="str">
-        <v>00101011010011100000000110101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C216" t="b">
         <v>0</v>
       </c>
       <c r="D216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>00000000000000000000000011000011</v>
+        <v>00000000000000000000000000101111</v>
       </c>
       <c r="B217" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -4719,16 +4719,16 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>00101011010011100000000110110000</v>
+        <v>00000000000000000000000011101110</v>
       </c>
       <c r="B218" t="str">
-        <v>00101011010011100000000110110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C218" t="b">
         <v>0</v>
       </c>
       <c r="D218">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>00000000000000000000000011111100</v>
+        <v>00000000000000000000000001000111</v>
       </c>
       <c r="B219" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4759,16 +4759,16 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>00101011010011100000000110110100</v>
+        <v>00000000000000000000000000011101</v>
       </c>
       <c r="B220" t="str">
-        <v>00101011010011100000000110110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C220" t="b">
         <v>0</v>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>00101011010011100000000110110110</v>
+        <v>00000000000000000000000011011000</v>
       </c>
       <c r="B221" t="str">
-        <v>00101011010011100000000110110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C221" t="b">
         <v>0</v>
@@ -4799,7 +4799,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>00000000000000000000000100011001</v>
+        <v>00000000000000000000000010111101</v>
       </c>
       <c r="B222" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -4819,7 +4819,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>00000000000000000000000011010011</v>
+        <v>00000000000000000000000011100101</v>
       </c>
       <c r="B223" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4828,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -4839,16 +4839,16 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>00101011010011100000000110111100</v>
+        <v>00000000000000000000000010011000</v>
       </c>
       <c r="B224" t="str">
-        <v>00101011010011100000000110111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C224" t="b">
         <v>0</v>
       </c>
       <c r="D224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -4859,16 +4859,16 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>00101011010011100000000110111110</v>
+        <v>00000000000000000000000010101111</v>
       </c>
       <c r="B225" t="str">
-        <v>00101011010011100000000110111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C225" t="b">
         <v>0</v>
       </c>
       <c r="D225">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -4879,16 +4879,16 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>00101011010011100000000111000000</v>
+        <v>00000000000000000000000011000010</v>
       </c>
       <c r="B226" t="str">
-        <v>00101011010011100000000111000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C226" t="b">
         <v>0</v>
       </c>
       <c r="D226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>00000000000000000000000011011001</v>
+        <v>00000000000000000000000011000110</v>
       </c>
       <c r="B227" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="D227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>00101011010011100000000111000100</v>
+        <v>00000000000000000000000011001000</v>
       </c>
       <c r="B228" t="str">
-        <v>00101011010011100000000111000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C228" t="b">
         <v>0</v>
@@ -4939,16 +4939,16 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>00101011010011100000000111000110</v>
+        <v>00000000000000000000000010100010</v>
       </c>
       <c r="B229" t="str">
-        <v>00101011010011100000000111000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C229" t="b">
         <v>0</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -4959,16 +4959,16 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>00101011010011100000000111001000</v>
+        <v>00000000000000000000000010110111</v>
       </c>
       <c r="B230" t="str">
-        <v>00101011010011100000000111001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C230" t="b">
         <v>0</v>
       </c>
       <c r="D230">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -4979,16 +4979,16 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>00101011010011100000000111001010</v>
+        <v>00000000000000000000000011001100</v>
       </c>
       <c r="B231" t="str">
-        <v>00101011010011100000000111001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C231" t="b">
         <v>0</v>
       </c>
       <c r="D231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>00101011010011100000000111001100</v>
+        <v>00000000000000000000000000000011</v>
       </c>
       <c r="B232" t="str">
-        <v>00101011010011100000000111001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C232" t="b">
         <v>0</v>
@@ -5019,16 +5019,16 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>00101011010011100000000111001110</v>
+        <v>00000000000000000000000000100111</v>
       </c>
       <c r="B233" t="str">
-        <v>00101011010011100000000111001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C233" t="b">
         <v>0</v>
       </c>
       <c r="D233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -5039,10 +5039,10 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>00101011010011100000000111010000</v>
+        <v>00000000000000000000000011001010</v>
       </c>
       <c r="B234" t="str">
-        <v>00101011010011100000000111010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C234" t="b">
         <v>0</v>
@@ -5059,16 +5059,16 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>00101011010011100000000111010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="B235" t="str">
-        <v>00101011010011100000000111010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C235" t="b">
         <v>0</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -5079,10 +5079,10 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>00101011010011100000000111010100</v>
+        <v>00000000000000000000000000011111</v>
       </c>
       <c r="B236" t="str">
-        <v>00101011010011100000000111010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C236" t="b">
         <v>0</v>
@@ -5099,16 +5099,16 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>00101011010011100000000111010110</v>
+        <v>00000000000000000000000011110001</v>
       </c>
       <c r="B237" t="str">
-        <v>00101011010011100000000111010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C237" t="b">
         <v>0</v>
       </c>
       <c r="D237">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>00101011010011100000000111011000</v>
+        <v>00000000000000000000000000011001</v>
       </c>
       <c r="B238" t="str">
-        <v>00101011010011100000000111011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C238" t="b">
         <v>0</v>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>00101011010011100000000111011010</v>
+        <v>00000000000000000000000001100000</v>
       </c>
       <c r="B239" t="str">
-        <v>00101011010011100000000111011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C239" t="b">
         <v>0</v>
@@ -5159,7 +5159,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>00000000000000000000000011000111</v>
+        <v>00000000000000000000000011011101</v>
       </c>
       <c r="B240" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5168,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -5179,16 +5179,16 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>00101011010011100000000111011110</v>
+        <v>00000000000000000000000001000100</v>
       </c>
       <c r="B241" t="str">
-        <v>00101011010011100000000111011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C241" t="b">
         <v>0</v>
       </c>
       <c r="D241">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -5199,16 +5199,16 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>00101011010011100000000111100000</v>
+        <v>00000000000000000000000010110100</v>
       </c>
       <c r="B242" t="str">
-        <v>00101011010011100000000111100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C242" t="b">
         <v>0</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -5219,16 +5219,16 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>00101011010011100000000111100010</v>
+        <v>00000000000000000000000011101001</v>
       </c>
       <c r="B243" t="str">
-        <v>00101011010011100000000111100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C243" t="b">
         <v>0</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -5239,7 +5239,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>00000000000000000000000001010111</v>
+        <v>00000000000000000000000010001010</v>
       </c>
       <c r="B244" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5259,16 +5259,16 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>00101011010011100000000111100110</v>
+        <v>00000000000000000000000011010000</v>
       </c>
       <c r="B245" t="str">
-        <v>00101011010011100000000111100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C245" t="b">
         <v>0</v>
       </c>
       <c r="D245">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -5279,16 +5279,16 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>00101011010011100000000111101000</v>
+        <v>00000000000000000000000001011001</v>
       </c>
       <c r="B246" t="str">
-        <v>00101011010011100000000111101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C246" t="b">
         <v>0</v>
       </c>
       <c r="D246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -5299,16 +5299,16 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>00101011010011100000000111101010</v>
+        <v>00000000000000000000000010010000</v>
       </c>
       <c r="B247" t="str">
-        <v>00101011010011100000000111101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C247" t="b">
         <v>0</v>
       </c>
       <c r="D247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -5319,16 +5319,16 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>00101011010011100000000111101100</v>
+        <v>00000000000000000000000001011000</v>
       </c>
       <c r="B248" t="str">
-        <v>00101011010011100000000111101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C248" t="b">
         <v>0</v>
       </c>
       <c r="D248">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>00101011010011100000000111101110</v>
+        <v>00000000000000000000000000011110</v>
       </c>
       <c r="B249" t="str">
-        <v>00101011010011100000000111101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C249" t="b">
         <v>0</v>
@@ -5359,16 +5359,16 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>00101011010011100000000111110000</v>
+        <v>00000000000000000000000001000110</v>
       </c>
       <c r="B250" t="str">
-        <v>00101011010011100000000111110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C250" t="b">
         <v>0</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>00101011010011100000000111110010</v>
+        <v>00000000000000000000000011111100</v>
       </c>
       <c r="B251" t="str">
-        <v>00101011010011100000000111110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C251" t="b">
         <v>0</v>
@@ -5399,16 +5399,16 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>00101011010011100000000111110100</v>
+        <v>00000000000000000000000011111001</v>
       </c>
       <c r="B252" t="str">
-        <v>00101011010011100000000111110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C252" t="b">
         <v>0</v>
       </c>
       <c r="D252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -5419,16 +5419,16 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>00101011010011100000000111110110</v>
+        <v>00000000000000000000000011111010</v>
       </c>
       <c r="B253" t="str">
-        <v>00101011010011100000000111110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C253" t="b">
         <v>0</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>00000000000000000000000011101110</v>
+        <v>00000000000000000000000011111000</v>
       </c>
       <c r="B254" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -5459,16 +5459,16 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>00101011010011100000000111111010</v>
+        <v>00000000000000000000000011111011</v>
       </c>
       <c r="B255" t="str">
-        <v>00101011010011100000000111111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C255" t="b">
         <v>0</v>
       </c>
       <c r="D255">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -5479,16 +5479,16 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>00101011010011100000000111111100</v>
+        <v>00000000000000000000000011111111</v>
       </c>
       <c r="B256" t="str">
-        <v>00101011010011100000000111111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C256" t="b">
         <v>0</v>
       </c>
       <c r="D256">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -5499,7 +5499,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>00000000000000000000000011011101</v>
+        <v>00000000000000000000000011111101</v>
       </c>
       <c r="B257" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -5519,16 +5519,16 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>00101011010011100000001000000000</v>
+        <v>00000000000000000000000100000001</v>
       </c>
       <c r="B258" t="str">
-        <v>00101011010011100000001000000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C258" t="b">
         <v>0</v>
       </c>
       <c r="D258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>00000000000000000000000100101000</v>
+        <v>00000000000000000000000011111110</v>
       </c>
       <c r="B259" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5548,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -5559,16 +5559,16 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>00101011010011100000001000000100</v>
+        <v>00000000000000000000000100000011</v>
       </c>
       <c r="B260" t="str">
-        <v>00101011010011100000001000000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C260" t="b">
         <v>0</v>
       </c>
       <c r="D260">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -5579,16 +5579,16 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>00101011010011100000001000000110</v>
+        <v>00000000000000000000000100000000</v>
       </c>
       <c r="B261" t="str">
-        <v>00101011010011100000001000000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C261" t="b">
         <v>0</v>
       </c>
       <c r="D261">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -5599,16 +5599,16 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>00101011010011100000001000001000</v>
+        <v>00000000000000000000000100000101</v>
       </c>
       <c r="B262" t="str">
-        <v>00101011010011100000001000001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C262" t="b">
         <v>0</v>
       </c>
       <c r="D262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -5619,16 +5619,16 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>00101011010011100000001000001010</v>
+        <v>00000000000000000000000100000010</v>
       </c>
       <c r="B263" t="str">
-        <v>00101011010011100000001000001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C263" t="b">
         <v>0</v>
       </c>
       <c r="D263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>00101011010011100000011111001011</v>
+        <v>00000000000000000000000100000100</v>
       </c>
       <c r="B264" t="str">
-        <v>00101011010011100000011111001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C264" t="b">
         <v>0</v>
@@ -5659,16 +5659,16 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>00101011010011100000011111001101</v>
+        <v>00000000000000000000000100000110</v>
       </c>
       <c r="B265" t="str">
-        <v>00101011010011100000011111001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C265" t="b">
         <v>0</v>
       </c>
       <c r="D265">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -5679,16 +5679,16 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>00101011010011100000001000001100</v>
+        <v>00000000000000000000000010101101</v>
       </c>
       <c r="B266" t="str">
-        <v>00101011010011100000001000001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C266" t="b">
         <v>0</v>
       </c>
       <c r="D266">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -5699,36 +5699,36 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>00101011010011100000001000001110</v>
+        <v>00000000000000000000000100000111</v>
       </c>
       <c r="B267" t="str">
-        <v>00101011010011100000001000001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C267" t="b">
         <v>0</v>
       </c>
       <c r="D267">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E267">
         <v>0</v>
       </c>
       <c r="F267">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>00101011010011100000001000010000</v>
+        <v>00000000000000000000000100001011</v>
       </c>
       <c r="B268" t="str">
-        <v>00101011010011100000001000010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C268" t="b">
         <v>0</v>
       </c>
       <c r="D268">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -5739,16 +5739,16 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>00101011010011100000001000010010</v>
+        <v>00000000000000000000000100001100</v>
       </c>
       <c r="B269" t="str">
-        <v>00101011010011100000001000010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C269" t="b">
         <v>0</v>
       </c>
       <c r="D269">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -5759,16 +5759,16 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>00101011010011100000001000010100</v>
+        <v>00000000000000000000000100001101</v>
       </c>
       <c r="B270" t="str">
-        <v>00101011010011100000001000010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C270" t="b">
         <v>0</v>
       </c>
       <c r="D270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -5779,16 +5779,16 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>00101011010011100000001000010110</v>
+        <v>00000000000000000000000100001110</v>
       </c>
       <c r="B271" t="str">
-        <v>00101011010011100000001000010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C271" t="b">
         <v>0</v>
       </c>
       <c r="D271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -5799,16 +5799,16 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>00101011010011100000001000011000</v>
+        <v>00000000000000000000000100001111</v>
       </c>
       <c r="B272" t="str">
-        <v>00101011010011100000001000011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C272" t="b">
         <v>0</v>
       </c>
       <c r="D272">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -5819,16 +5819,16 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>00101011010011100000001000011010</v>
+        <v>00000000000000000000000100010000</v>
       </c>
       <c r="B273" t="str">
-        <v>00101011010011100000001000011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C273" t="b">
         <v>0</v>
       </c>
       <c r="D273">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -5839,16 +5839,16 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>00101011010011100000001000011100</v>
+        <v>00000000000000000000000100010001</v>
       </c>
       <c r="B274" t="str">
-        <v>00101011010011100000001000011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C274" t="b">
         <v>0</v>
       </c>
       <c r="D274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -5859,16 +5859,16 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>00101011010011100000001000011110</v>
+        <v>00000000000000000000000100010010</v>
       </c>
       <c r="B275" t="str">
-        <v>00101011010011100000001000011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C275" t="b">
         <v>0</v>
       </c>
       <c r="D275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -5879,16 +5879,16 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>00101011010011100000001000100000</v>
+        <v>00000000000000000000000100010011</v>
       </c>
       <c r="B276" t="str">
-        <v>00101011010011100000001000100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C276" t="b">
         <v>0</v>
       </c>
       <c r="D276">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -5899,16 +5899,16 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>00101011010011100000001000100010</v>
+        <v>00000000000000000000000100010100</v>
       </c>
       <c r="B277" t="str">
-        <v>00101011010011100000001000100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C277" t="b">
         <v>0</v>
       </c>
       <c r="D277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -5919,16 +5919,16 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>00101011010011100000001000100100</v>
+        <v>00000000000000000000000100010101</v>
       </c>
       <c r="B278" t="str">
-        <v>00101011010011100000001000100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C278" t="b">
         <v>0</v>
       </c>
       <c r="D278">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -5939,16 +5939,16 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>00101011010011100000001000100110</v>
+        <v>00000000000000000000000100010110</v>
       </c>
       <c r="B279" t="str">
-        <v>00101011010011100000001000100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C279" t="b">
         <v>0</v>
       </c>
       <c r="D279">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -5959,16 +5959,16 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>00101011010011100000001000101000</v>
+        <v>00000000000000000000000100010111</v>
       </c>
       <c r="B280" t="str">
-        <v>00101011010011100000001000101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C280" t="b">
         <v>0</v>
       </c>
       <c r="D280">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -5979,16 +5979,16 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>00101011010011100000001000101010</v>
+        <v>00000000000000000000000100011000</v>
       </c>
       <c r="B281" t="str">
-        <v>00101011010011100000001000101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C281" t="b">
         <v>0</v>
       </c>
       <c r="D281">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -5999,16 +5999,16 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>00101011010011100000001000101100</v>
+        <v>00000000000000000000000100011001</v>
       </c>
       <c r="B282" t="str">
-        <v>00101011010011100000001000101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C282" t="b">
         <v>0</v>
       </c>
       <c r="D282">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>00000000000000000000000000110111</v>
+        <v>00000000000000000000000100011010</v>
       </c>
       <c r="B283" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6028,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>00000000000000000000000010110000</v>
+        <v>00000000000000000000000100011011</v>
       </c>
       <c r="B284" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -6059,16 +6059,16 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>00101011010011100000001000110010</v>
+        <v>00000000000000000000000100011100</v>
       </c>
       <c r="B285" t="str">
-        <v>00101011010011100000001000110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C285" t="b">
         <v>0</v>
       </c>
       <c r="D285">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -6079,7 +6079,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>00000000000000000000000010100000</v>
+        <v>00000000000000000000000100011101</v>
       </c>
       <c r="B286" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6088,7 +6088,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -6099,16 +6099,16 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>00101011010011100000001000110110</v>
+        <v>00000000000000000000000100011110</v>
       </c>
       <c r="B287" t="str">
-        <v>00101011010011100000001000110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C287" t="b">
         <v>0</v>
       </c>
       <c r="D287">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -6119,16 +6119,16 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>00101011010011100000001000111000</v>
+        <v>00000000000000000000000100011111</v>
       </c>
       <c r="B288" t="str">
-        <v>00101011010011100000001000111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C288" t="b">
         <v>0</v>
       </c>
       <c r="D288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -6139,16 +6139,16 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>00101011010011100000001000111010</v>
+        <v>00000000000000000000000100100000</v>
       </c>
       <c r="B289" t="str">
-        <v>00101011010011100000001000111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C289" t="b">
         <v>0</v>
       </c>
       <c r="D289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -6159,16 +6159,16 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>00101011010011100000001000111100</v>
+        <v>00000000000000000000000100100001</v>
       </c>
       <c r="B290" t="str">
-        <v>00101011010011100000001000111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C290" t="b">
         <v>0</v>
       </c>
       <c r="D290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -6179,16 +6179,16 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>00101011010011100000001000111110</v>
+        <v>00000000000000000000000100100010</v>
       </c>
       <c r="B291" t="str">
-        <v>00101011010011100000001000111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C291" t="b">
         <v>0</v>
       </c>
       <c r="D291">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -6199,16 +6199,16 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>00101011010011100000001001000000</v>
+        <v>00000000000000000000000100100011</v>
       </c>
       <c r="B292" t="str">
-        <v>00101011010011100000001001000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C292" t="b">
         <v>0</v>
       </c>
       <c r="D292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -6219,16 +6219,16 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>00101011010011100000001001000010</v>
+        <v>00000000000000000000000100100100</v>
       </c>
       <c r="B293" t="str">
-        <v>00101011010011100000001001000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C293" t="b">
         <v>0</v>
       </c>
       <c r="D293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -6239,16 +6239,16 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>00101011010011100000001001000100</v>
+        <v>00000000000000000000000100100101</v>
       </c>
       <c r="B294" t="str">
-        <v>00101011010011100000001001000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C294" t="b">
         <v>0</v>
       </c>
       <c r="D294">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -6259,16 +6259,16 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>00101011010011100000001001000110</v>
+        <v>00000000000000000000000100100110</v>
       </c>
       <c r="B295" t="str">
-        <v>00101011010011100000001001000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C295" t="b">
         <v>0</v>
       </c>
       <c r="D295">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -6279,16 +6279,16 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>00101011010011100000001001001000</v>
+        <v>00000000000000000000000100100111</v>
       </c>
       <c r="B296" t="str">
-        <v>00101011010011100000001001001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C296" t="b">
         <v>0</v>
       </c>
       <c r="D296">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -6299,16 +6299,16 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>00101011010011100000001001001010</v>
+        <v>00000000000000000000000100101000</v>
       </c>
       <c r="B297" t="str">
-        <v>00101011010011100000001001001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C297" t="b">
         <v>0</v>
       </c>
       <c r="D297">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -6319,7 +6319,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>00000000000000000000000000110010</v>
+        <v>00000000000000000000000100101001</v>
       </c>
       <c r="B298" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E298">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>00000000000000000000000011001000</v>
+        <v>00000000000000000000000100101010</v>
       </c>
       <c r="B299" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6348,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -6359,16 +6359,16 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>00101011010011100000011111000111</v>
+        <v>00000000000000000000000100101011</v>
       </c>
       <c r="B300" t="str">
-        <v>00101011010011100000011111000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C300" t="b">
         <v>0</v>
       </c>
       <c r="D300">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -6379,16 +6379,16 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>00101011010011100000011111000101</v>
+        <v>00000000000000000000000100101100</v>
       </c>
       <c r="B301" t="str">
-        <v>00101011010011100000011111000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C301" t="b">
         <v>0</v>
       </c>
       <c r="D301">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E301">
         <v>0</v>
